--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 유닛 하나(플레이어·몬스터·보스 공통 스탯). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음.</t>
+          <t>한 행 = 유닛 하나(플레이어·몬스터·보스 공통 스탯). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>

--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 유닛 하나(플레이어·몬스터·보스 공통 스탯). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음.</t>
+          <t>한 행 = 유닛 하나(플레이어·몬스터·보스 공통 스탯). Type은 Player·Monster·Elite·Boss(Elite는 10/29 초안, 상태 단계는 EliteState). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>

--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.88" customWidth="1" min="1" max="1"/>
@@ -642,11 +642,6 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -694,11 +689,6 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
           <t>주인공. 성장 없음(10/28)</t>
         </is>
       </c>
@@ -749,11 +739,6 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
           <t>잡몹</t>
         </is>
       </c>
@@ -804,11 +789,6 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
           <t>잡몹</t>
         </is>
       </c>
@@ -859,11 +839,6 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
           <t>변종, 지스타 포함 여부 미정</t>
         </is>
       </c>
@@ -914,11 +889,6 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
           <t>변종, 지스타 포함 여부 미정</t>
         </is>
       </c>
@@ -965,11 +935,6 @@
         <v>200</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>보스. 곡선 밖 개별 값</t>
         </is>

--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>체력·공격·방어·회피 확률·치명타·체세·이동 속도.</t>
+          <t>CSV,체력·공격·방어·회피 확률·치명타·체세·이동 속도.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 유닛 하나(플레이어·몬스터·보스 공통 스탯). Type은 Player·Monster·Elite·Boss(Elite는 10/29 초안, 상태 단계는 EliteState). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음.</t>
+          <t>한 행 = 유닛 하나(플레이어·몬스터·엘리트·보스 공통 스탯, 모든 유닛이 같은 열). Type은 Player·Monster·Elite·Boss(Elite는 10/29 초안, 상태 단계는 EliteState). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음. 아이템 스탯 JSON의 statType도 이 열 이름과 똑같이 씀.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Player·Monster·Boss·Attack이 이 ID(UnitID·OwnerID)로 가리킨다. 전투 계산과 Balance 탭이 읽는다.</t>
+          <t>Player·Monster·BossState·EliteState·PlayerState가 이 ID(UnitID)로 가리킨다. 전투 계산과 Balance 탭이 읽는다.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>배율(Attack)</t>
+          <t>배율(가정)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.88" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 유닛 하나(플레이어·몬스터·엘리트·보스 공통 스탯, 모든 유닛이 같은 열). Type은 Player·Monster·Elite·Boss(Elite는 10/29 초안, 상태 단계는 EliteState). 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음. 아이템 스탯 JSON의 statType도 이 열 이름과 똑같이 씀.</t>
+          <t>한 행 = 유닛 하나(플레이어·몬스터·엘리트·보스 공통 스탯, 모든 유닛이 같은 열). Type은 Player·Monster·Elite·Boss(Elite는 10/29 초안, 상태 단계는 EliteState). DEF는 고정 수치(데미지에서 뺀, 10/29), ArmorPen은 방어구 관통(고정 수치, 대상 DEF를 그만큼 무시). 공식은 Formula 탭. 비율은 만분율(10000=100%), MoveSpeed는 타일×100/초(600=초당 6타일). Crit = 치명타 확률(만분율, 1000=10%), CritMult = 치명타가 터졌을 때 데미지 배율(만분율, 15000=1.5배). 몬스터 HP·ATK·DEF·Dodge·Poise는 StatCurve 등급(Tier) 값. 16행부터의 계산 예시는 내보내지 않음. 아이템 스탯 JSON과 Buff의 statType도 이 열 이름과 똑같이 씀.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>CSV,체력·공격·방어·회피 확률·치명타·체세·이동 속도.</t>
+          <t>CSV,체력·공격·방어·회피 확률·치명타·체세·이동 속도·방어구 관통.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -642,6 +642,11 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
+          <t>ArmorPen</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
@@ -687,7 +692,10 @@
       <c r="M7" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>주인공. 성장 없음(10/28)</t>
         </is>
@@ -737,7 +745,10 @@
       <c r="M8" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>잡몹</t>
         </is>
@@ -770,7 +781,7 @@
         <v>26</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>400</v>
@@ -787,7 +798,10 @@
       <c r="M9" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>잡몹</t>
         </is>
@@ -820,7 +834,7 @@
         <v>32</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>500</v>
@@ -837,7 +851,10 @@
       <c r="M10" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>변종, 지스타 포함 여부 미정</t>
         </is>
@@ -870,7 +887,7 @@
         <v>32</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>500</v>
@@ -887,7 +904,10 @@
       <c r="M11" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>변종, 지스타 포함 여부 미정</t>
         </is>
@@ -917,7 +937,7 @@
         <v>28</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>300</v>
@@ -934,7 +954,10 @@
       <c r="M12" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>보스. 곡선 밖 개별 값</t>
         </is>
@@ -954,7 +977,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>계산 예시 (전투 기획서 C05 공식, 위 표 값으로 자동 계산, 내보내지 않음)</t>
+          <t>계산 예시 (Formula 탭 공식: 데미지 = max(1, INT(ATK×배율) − DEF) → 치명타 배율, 아이템 ATK 없이. 위 표 값으로 자동 계산, 내보내지 않음)</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1029,16 +1052,16 @@
         <v>10000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -1062,16 +1085,16 @@
         <v>15000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>420</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>

--- a/tables/UnitStat.xlsx
+++ b/tables/UnitStat.xlsx
@@ -686,7 +686,7 @@
         <v>100</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>500</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>6</v>
@@ -711,7 +711,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>주인공. 성장 없음(10/28)</t>
+          <t>주인공. 성장 없음(10/28). 지스타는 버선칼 스탯(ATK+2, Crit+200)을 여기에 임시로 합침(ATK 10→12, Crit 1000→1200). 완성판에서 Item으로 분리(10/30)</t>
         </is>
       </c>
     </row>
@@ -977,6 +977,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
@@ -1057,7 +1059,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>0</v>
@@ -1069,13 +1071,13 @@
         <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -1090,7 +1092,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>10</v>
@@ -1102,13 +1104,13 @@
         <v>4</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>420</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
